--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/65.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/65.xlsx
@@ -426,13 +426,13 @@
         <v>-5.164405987990824</v>
       </c>
       <c r="E2">
-        <v>-12.66382929081104</v>
+        <v>-11.04527715220079</v>
       </c>
       <c r="F2">
-        <v>-2.379767985073442</v>
+        <v>-2.218067354577367</v>
       </c>
       <c r="G2">
-        <v>-8.235770799129973</v>
+        <v>-7.579772921837824</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.262635023062241</v>
       </c>
       <c r="E3">
-        <v>-11.49355816975748</v>
+        <v>-12.96956378927697</v>
       </c>
       <c r="F3">
-        <v>-2.789059348592261</v>
+        <v>-2.03475047670524</v>
       </c>
       <c r="G3">
-        <v>-8.678510004497033</v>
+        <v>-6.662730608997145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.550313084300571</v>
       </c>
       <c r="E4">
-        <v>-13.34740634276457</v>
+        <v>-12.56937695886179</v>
       </c>
       <c r="F4">
-        <v>-3.130591086929484</v>
+        <v>-2.270025871550564</v>
       </c>
       <c r="G4">
-        <v>-7.360389443101984</v>
+        <v>-6.383407045193935</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.139461732813081</v>
       </c>
       <c r="E5">
-        <v>-13.57300047550661</v>
+        <v>-13.16378456367125</v>
       </c>
       <c r="F5">
-        <v>-2.714615626837475</v>
+        <v>-2.213685291016558</v>
       </c>
       <c r="G5">
-        <v>-7.999943545587006</v>
+        <v>-6.478367658206498</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.985391040370368</v>
       </c>
       <c r="E6">
-        <v>-14.76706534424011</v>
+        <v>-13.84757342940235</v>
       </c>
       <c r="F6">
-        <v>-2.567791646528277</v>
+        <v>-2.189742159606041</v>
       </c>
       <c r="G6">
-        <v>-6.486680268984603</v>
+        <v>-6.431134067064076</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.073319505624376</v>
       </c>
       <c r="E7">
-        <v>-14.55413019961615</v>
+        <v>-14.1375547973132</v>
       </c>
       <c r="F7">
-        <v>-2.837894920456903</v>
+        <v>-2.050827431258773</v>
       </c>
       <c r="G7">
-        <v>-7.361026464782215</v>
+        <v>-5.833714771535032</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.347622350416083</v>
       </c>
       <c r="E8">
-        <v>-15.8125200053486</v>
+        <v>-14.68892682637479</v>
       </c>
       <c r="F8">
-        <v>-2.159801648199256</v>
+        <v>-1.42453528616779</v>
       </c>
       <c r="G8">
-        <v>-6.267944254907358</v>
+        <v>-5.91440244386798</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.760835503428772</v>
       </c>
       <c r="E9">
-        <v>-16.04712245345419</v>
+        <v>-15.53271815839491</v>
       </c>
       <c r="F9">
-        <v>-2.102717193737536</v>
+        <v>-1.471126810738248</v>
       </c>
       <c r="G9">
-        <v>-6.645643285648308</v>
+        <v>-5.867270671764611</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.251640835955334</v>
       </c>
       <c r="E10">
-        <v>-16.54254241954769</v>
+        <v>-16.40223448136101</v>
       </c>
       <c r="F10">
-        <v>-1.903455071728921</v>
+        <v>-1.311979208577601</v>
       </c>
       <c r="G10">
-        <v>-6.956828376441465</v>
+        <v>-5.507831188693907</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.762726425986126</v>
       </c>
       <c r="E11">
-        <v>-17.63725832017997</v>
+        <v>-17.04936710393917</v>
       </c>
       <c r="F11">
-        <v>-1.7705021035796</v>
+        <v>-1.08493944245091</v>
       </c>
       <c r="G11">
-        <v>-5.734375939843172</v>
+        <v>-5.62326265004539</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.243730775414375</v>
       </c>
       <c r="E12">
-        <v>-18.12127772118681</v>
+        <v>-17.01485391782984</v>
       </c>
       <c r="F12">
-        <v>-0.9653430703043284</v>
+        <v>-0.7908110287388894</v>
       </c>
       <c r="G12">
-        <v>-7.120723089637784</v>
+        <v>-5.950535149008988</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.651216686978487</v>
       </c>
       <c r="E13">
-        <v>-19.8203107888496</v>
+        <v>-18.44430619160933</v>
       </c>
       <c r="F13">
-        <v>-1.506249588616947</v>
+        <v>-0.7015842623137434</v>
       </c>
       <c r="G13">
-        <v>-6.230856017246003</v>
+        <v>-5.428991923531468</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.957353717744753</v>
       </c>
       <c r="E14">
-        <v>-20.28170349455878</v>
+        <v>-18.64425839763188</v>
       </c>
       <c r="F14">
-        <v>-1.072769896936382</v>
+        <v>-0.2864678192184384</v>
       </c>
       <c r="G14">
-        <v>-5.490362696634769</v>
+        <v>-5.332950462258184</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.155359807041848</v>
       </c>
       <c r="E15">
-        <v>-21.28097444573517</v>
+        <v>-20.00831005267929</v>
       </c>
       <c r="F15">
-        <v>-0.891012834883726</v>
+        <v>-0.08181716725461212</v>
       </c>
       <c r="G15">
-        <v>-6.185833726772255</v>
+        <v>-5.329901112575763</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.253115832554673</v>
       </c>
       <c r="E16">
-        <v>-21.02134059297484</v>
+        <v>-19.62517215475253</v>
       </c>
       <c r="F16">
-        <v>-0.1580054307596938</v>
+        <v>0.2188006766909397</v>
       </c>
       <c r="G16">
-        <v>-5.843168277699453</v>
+        <v>-4.611416368867614</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.277941319390012</v>
       </c>
       <c r="E17">
-        <v>-21.66569056396537</v>
+        <v>-20.82139669337495</v>
       </c>
       <c r="F17">
-        <v>-0.2840365608912218</v>
+        <v>0.3994734058133315</v>
       </c>
       <c r="G17">
-        <v>-5.586111754513849</v>
+        <v>-4.943275946077797</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.263561631339288</v>
       </c>
       <c r="E18">
-        <v>-22.53894477712381</v>
+        <v>-22.66211656538426</v>
       </c>
       <c r="F18">
-        <v>0.1132119973256979</v>
+        <v>1.044681320547241</v>
       </c>
       <c r="G18">
-        <v>-5.782285713834692</v>
+        <v>-4.631171873188569</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.238849391430548</v>
       </c>
       <c r="E19">
-        <v>-23.39790779011353</v>
+        <v>-23.11956372033485</v>
       </c>
       <c r="F19">
-        <v>0.4645598893860942</v>
+        <v>1.157284615079389</v>
       </c>
       <c r="G19">
-        <v>-5.338584449085807</v>
+        <v>-4.748438687987604</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.235362275748954</v>
       </c>
       <c r="E20">
-        <v>-25.38933939467822</v>
+        <v>-23.0268515839307</v>
       </c>
       <c r="F20">
-        <v>0.7443467782534469</v>
+        <v>1.587591659607231</v>
       </c>
       <c r="G20">
-        <v>-4.339222748542734</v>
+        <v>-4.500013286420219</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.268916089532533</v>
       </c>
       <c r="E21">
-        <v>-25.1220137945443</v>
+        <v>-23.40816206887453</v>
       </c>
       <c r="F21">
-        <v>0.6387937186865255</v>
+        <v>2.028803332625527</v>
       </c>
       <c r="G21">
-        <v>-5.38286789884027</v>
+        <v>-4.646601373722048</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.34946546088454</v>
       </c>
       <c r="E22">
-        <v>-25.8191344686281</v>
+        <v>-24.6732634641079</v>
       </c>
       <c r="F22">
-        <v>0.9470565653925138</v>
+        <v>2.319469170593845</v>
       </c>
       <c r="G22">
-        <v>-5.465307380793854</v>
+        <v>-4.84284321240226</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.479630867137923</v>
       </c>
       <c r="E23">
-        <v>-26.42154946487183</v>
+        <v>-24.99493798763852</v>
       </c>
       <c r="F23">
-        <v>1.43320054307346</v>
+        <v>2.380400563274165</v>
       </c>
       <c r="G23">
-        <v>-4.97090806683014</v>
+        <v>-5.314341074812728</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.649182881180985</v>
       </c>
       <c r="E24">
-        <v>-26.85060942041721</v>
+        <v>-25.50835797161383</v>
       </c>
       <c r="F24">
-        <v>2.123561936566567</v>
+        <v>2.916304570841278</v>
       </c>
       <c r="G24">
-        <v>-5.044045465805588</v>
+        <v>-4.450633663223902</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.854956769838994</v>
       </c>
       <c r="E25">
-        <v>-25.87602100414427</v>
+        <v>-25.67249703638237</v>
       </c>
       <c r="F25">
-        <v>1.84875933436186</v>
+        <v>2.755554906123617</v>
       </c>
       <c r="G25">
-        <v>-5.355400254997167</v>
+        <v>-4.853526379269096</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.086039681541475</v>
       </c>
       <c r="E26">
-        <v>-25.97360485743244</v>
+        <v>-25.85736062566182</v>
       </c>
       <c r="F26">
-        <v>1.8397168757929</v>
+        <v>3.393720869566328</v>
       </c>
       <c r="G26">
-        <v>-5.071004014453424</v>
+        <v>-5.18114349651872</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.336448168104132</v>
       </c>
       <c r="E27">
-        <v>-27.01979463694543</v>
+        <v>-25.97034458654246</v>
       </c>
       <c r="F27">
-        <v>2.089337108952503</v>
+        <v>3.238204830099555</v>
       </c>
       <c r="G27">
-        <v>-5.91810970118736</v>
+        <v>-5.432289293950045</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.604837415393041</v>
       </c>
       <c r="E28">
-        <v>-28.75962885266333</v>
+        <v>-25.72642648543528</v>
       </c>
       <c r="F28">
-        <v>2.285976619763856</v>
+        <v>3.438580277897533</v>
       </c>
       <c r="G28">
-        <v>-6.238294028586084</v>
+        <v>-5.762522377279964</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.883835508586944</v>
       </c>
       <c r="E29">
-        <v>-26.26020966453621</v>
+        <v>-25.57747986769295</v>
       </c>
       <c r="F29">
-        <v>2.253895606988236</v>
+        <v>3.277366727434304</v>
       </c>
       <c r="G29">
-        <v>-6.131997562558907</v>
+        <v>-5.160688312647348</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.173778872183307</v>
       </c>
       <c r="E30">
-        <v>-25.92330946828877</v>
+        <v>-25.04252132978708</v>
       </c>
       <c r="F30">
-        <v>2.043773588328919</v>
+        <v>2.952207670813414</v>
       </c>
       <c r="G30">
-        <v>-5.791081312362152</v>
+        <v>-5.59917853119237</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.469969156052018</v>
       </c>
       <c r="E31">
-        <v>-26.42384619073446</v>
+        <v>-25.02155591901935</v>
       </c>
       <c r="F31">
-        <v>1.91652310138047</v>
+        <v>3.119145240029987</v>
       </c>
       <c r="G31">
-        <v>-5.478486419489794</v>
+        <v>-5.767819578055333</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.765353239163909</v>
       </c>
       <c r="E32">
-        <v>-25.60484122390092</v>
+        <v>-24.73435304948481</v>
       </c>
       <c r="F32">
-        <v>1.592341518294884</v>
+        <v>2.824388923826644</v>
       </c>
       <c r="G32">
-        <v>-6.066493980767875</v>
+        <v>-5.69617030349682</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.057552955588871</v>
       </c>
       <c r="E33">
-        <v>-24.13162656239171</v>
+        <v>-24.44286406586304</v>
       </c>
       <c r="F33">
-        <v>1.62272603462957</v>
+        <v>2.909523555281961</v>
       </c>
       <c r="G33">
-        <v>-5.246694071712392</v>
+        <v>-5.777844837285208</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.332821549187139</v>
       </c>
       <c r="E34">
-        <v>-25.33939702849715</v>
+        <v>-23.53238461960015</v>
       </c>
       <c r="F34">
-        <v>1.472216647745316</v>
+        <v>2.582846929579143</v>
       </c>
       <c r="G34">
-        <v>-5.087365550805931</v>
+        <v>-5.646699304239815</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.579829413979104</v>
       </c>
       <c r="E35">
-        <v>-23.90761064995311</v>
+        <v>-23.97976023708803</v>
       </c>
       <c r="F35">
-        <v>0.9571891554635574</v>
+        <v>2.571514863508845</v>
       </c>
       <c r="G35">
-        <v>-5.425872083745088</v>
+        <v>-5.386541216479967</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.783439097899118</v>
       </c>
       <c r="E36">
-        <v>-24.76881639705823</v>
+        <v>-23.92448099435456</v>
       </c>
       <c r="F36">
-        <v>1.100695524324544</v>
+        <v>2.429936933961576</v>
       </c>
       <c r="G36">
-        <v>-5.904669588032309</v>
+        <v>-5.016165324317089</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.925799928037389</v>
       </c>
       <c r="E37">
-        <v>-23.93907537895001</v>
+        <v>-22.94043571589499</v>
       </c>
       <c r="F37">
-        <v>1.224306164905091</v>
+        <v>2.371798796163496</v>
       </c>
       <c r="G37">
-        <v>-6.415237243248788</v>
+        <v>-5.672999945250689</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.998397493847232</v>
       </c>
       <c r="E38">
-        <v>-25.03250793728292</v>
+        <v>-22.07378095553169</v>
       </c>
       <c r="F38">
-        <v>1.358370802108969</v>
+        <v>1.989759063461975</v>
       </c>
       <c r="G38">
-        <v>-5.477353356337251</v>
+        <v>-5.547237767552171</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.98616116729386</v>
       </c>
       <c r="E39">
-        <v>-23.64579636124725</v>
+        <v>-21.66887607705151</v>
       </c>
       <c r="F39">
-        <v>1.7024497702098</v>
+        <v>1.747451657734286</v>
       </c>
       <c r="G39">
-        <v>-4.289438459934795</v>
+        <v>-4.539038696568181</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.884523969440163</v>
       </c>
       <c r="E40">
-        <v>-22.4357499353358</v>
+        <v>-20.42847382956689</v>
       </c>
       <c r="F40">
-        <v>1.258868966419498</v>
+        <v>1.77190009326051</v>
       </c>
       <c r="G40">
-        <v>-4.854233891053288</v>
+        <v>-4.483944153461917</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.690915771504493</v>
       </c>
       <c r="E41">
-        <v>-22.31403592425037</v>
+        <v>-20.96917625873499</v>
       </c>
       <c r="F41">
-        <v>0.3263741243532891</v>
+        <v>1.337482689679977</v>
       </c>
       <c r="G41">
-        <v>-5.431466909403844</v>
+        <v>-4.434050213581151</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.409044357009979</v>
       </c>
       <c r="E42">
-        <v>-21.69759968657402</v>
+        <v>-20.34217425144828</v>
       </c>
       <c r="F42">
-        <v>0.9986522574432838</v>
+        <v>1.24988615030354</v>
       </c>
       <c r="G42">
-        <v>-4.635633635694781</v>
+        <v>-4.047905424087949</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.054052087170341</v>
       </c>
       <c r="E43">
-        <v>-21.36915958179526</v>
+        <v>-19.27165080678312</v>
       </c>
       <c r="F43">
-        <v>1.056695961357445</v>
+        <v>1.133078062834782</v>
       </c>
       <c r="G43">
-        <v>-4.766951477883188</v>
+        <v>-4.061799806801854</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.63827858182059</v>
       </c>
       <c r="E44">
-        <v>-20.83436717234239</v>
+        <v>-19.69928205763277</v>
       </c>
       <c r="F44">
-        <v>0.8319863927348289</v>
+        <v>0.9187015491946867</v>
       </c>
       <c r="G44">
-        <v>-5.539175788254814</v>
+        <v>-3.786723924448385</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.186830567628007</v>
       </c>
       <c r="E45">
-        <v>-21.76923427550467</v>
+        <v>-19.12892985281671</v>
       </c>
       <c r="F45">
-        <v>0.4986124165803762</v>
+        <v>1.006583046957686</v>
       </c>
       <c r="G45">
-        <v>-5.073954155841381</v>
+        <v>-3.66493268927295</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.723367329948459</v>
       </c>
       <c r="E46">
-        <v>-20.42003865736616</v>
+        <v>-19.31295449340854</v>
       </c>
       <c r="F46">
-        <v>0.7362370613800396</v>
+        <v>0.7593087502828115</v>
       </c>
       <c r="G46">
-        <v>-5.183712469196375</v>
+        <v>-3.423927023833509</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.269464630447598</v>
       </c>
       <c r="E47">
-        <v>-21.07447262545337</v>
+        <v>-18.0514207067032</v>
       </c>
       <c r="F47">
-        <v>0.2971335834018693</v>
+        <v>0.8130946457465834</v>
       </c>
       <c r="G47">
-        <v>-4.887312025022693</v>
+        <v>-3.332519634209451</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.850985841842469</v>
       </c>
       <c r="E48">
-        <v>-19.25977677560544</v>
+        <v>-17.59884111542531</v>
       </c>
       <c r="F48">
-        <v>0.5803093233140747</v>
+        <v>0.6939720997544033</v>
       </c>
       <c r="G48">
-        <v>-4.776893193286147</v>
+        <v>-3.324958917873587</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.482691970190717</v>
       </c>
       <c r="E49">
-        <v>-18.42827479589549</v>
+        <v>-17.41747037687005</v>
       </c>
       <c r="F49">
-        <v>0.1557246408047713</v>
+        <v>0.530951879985669</v>
       </c>
       <c r="G49">
-        <v>-4.383166801500353</v>
+        <v>-3.60253067205616</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.178811499305705</v>
       </c>
       <c r="E50">
-        <v>-17.35932957153377</v>
+        <v>-17.45480359346893</v>
       </c>
       <c r="F50">
-        <v>-0.5164250953377896</v>
+        <v>0.5303513136186393</v>
       </c>
       <c r="G50">
-        <v>-4.95852530523449</v>
+        <v>-3.429023197275363</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.951397967394518</v>
       </c>
       <c r="E51">
-        <v>-19.36432141107402</v>
+        <v>-15.80364874595877</v>
       </c>
       <c r="F51">
-        <v>-0.3697369672826503</v>
+        <v>0.5004240560902988</v>
       </c>
       <c r="G51">
-        <v>-5.457490811488061</v>
+        <v>-3.170841443170988</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.800175795864766</v>
       </c>
       <c r="E52">
-        <v>-16.45024560427603</v>
+        <v>-16.11010590319522</v>
       </c>
       <c r="F52">
-        <v>-0.1242983327723792</v>
+        <v>0.2650997875682096</v>
       </c>
       <c r="G52">
-        <v>-4.880571082488438</v>
+        <v>-3.033479727254153</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.729107873814494</v>
       </c>
       <c r="E53">
-        <v>-16.14336066627312</v>
+        <v>-16.06541734934006</v>
       </c>
       <c r="F53">
-        <v>-0.5032316877134018</v>
+        <v>0.1803147271568746</v>
       </c>
       <c r="G53">
-        <v>-4.907704551023879</v>
+        <v>-2.756889613037838</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.733845858122758</v>
       </c>
       <c r="E54">
-        <v>-16.22904972232698</v>
+        <v>-15.14735829240936</v>
       </c>
       <c r="F54">
-        <v>-0.3031768181003072</v>
+        <v>0.0533740496170728</v>
       </c>
       <c r="G54">
-        <v>-4.325122117006131</v>
+        <v>-3.237029040044892</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.806298190176038</v>
       </c>
       <c r="E55">
-        <v>-16.09190653116982</v>
+        <v>-14.2907127713389</v>
       </c>
       <c r="F55">
-        <v>0.09216566672277084</v>
+        <v>-0.1084027906800595</v>
       </c>
       <c r="G55">
-        <v>-5.19265949091012</v>
+        <v>-3.539465525713228</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.942562266298845</v>
       </c>
       <c r="E56">
-        <v>-13.23080908803134</v>
+        <v>-14.18887187644278</v>
       </c>
       <c r="F56">
-        <v>-0.2252746624388333</v>
+        <v>0.1151246976587619</v>
       </c>
       <c r="G56">
-        <v>-4.367468394273989</v>
+        <v>-2.898070848291471</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.128667763941422</v>
       </c>
       <c r="E57">
-        <v>-15.85764464639287</v>
+        <v>-14.26029880480719</v>
       </c>
       <c r="F57">
-        <v>-0.4422265703342322</v>
+        <v>-0.2083892213001682</v>
       </c>
       <c r="G57">
-        <v>-4.170915876987434</v>
+        <v>-3.466738013638585</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.354402049296225</v>
       </c>
       <c r="E58">
-        <v>-14.52294373577802</v>
+        <v>-14.27329004983125</v>
       </c>
       <c r="F58">
-        <v>-0.2977824895732769</v>
+        <v>-0.1845761435718908</v>
       </c>
       <c r="G58">
-        <v>-4.692158866836975</v>
+        <v>-3.550227014917797</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.609917298256379</v>
       </c>
       <c r="E59">
-        <v>-13.67010670949242</v>
+        <v>-13.46480932049482</v>
       </c>
       <c r="F59">
-        <v>-0.8028033036292178</v>
+        <v>-0.2890357581671169</v>
       </c>
       <c r="G59">
-        <v>-5.112530517919671</v>
+        <v>-3.517704969546299</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.880190967736194</v>
       </c>
       <c r="E60">
-        <v>-14.86631878848087</v>
+        <v>-12.55122742537229</v>
       </c>
       <c r="F60">
-        <v>-1.211966270200603</v>
+        <v>-0.2086567839712724</v>
       </c>
       <c r="G60">
-        <v>-4.305781721075164</v>
+        <v>-3.889033783484932</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.156793653655584</v>
       </c>
       <c r="E61">
-        <v>-13.62837524210055</v>
+        <v>-12.62626764758929</v>
       </c>
       <c r="F61">
-        <v>-0.01587000995034068</v>
+        <v>-0.5906103664629021</v>
       </c>
       <c r="G61">
-        <v>-5.736519361152475</v>
+        <v>-3.712401247428572</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.43034285333818</v>
       </c>
       <c r="E62">
-        <v>-13.97739866220516</v>
+        <v>-12.24322527352301</v>
       </c>
       <c r="F62">
-        <v>-1.221925731484461</v>
+        <v>-0.6537104250037516</v>
       </c>
       <c r="G62">
-        <v>-4.480894803779496</v>
+        <v>-3.874692963445947</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.689990089387291</v>
       </c>
       <c r="E63">
-        <v>-13.90877515148502</v>
+        <v>-12.00898415480268</v>
       </c>
       <c r="F63">
-        <v>-0.6268183056392684</v>
+        <v>-0.9604151126250742</v>
       </c>
       <c r="G63">
-        <v>-5.165194457811609</v>
+        <v>-4.375929817493787</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.934911723938531</v>
       </c>
       <c r="E64">
-        <v>-11.96345665225991</v>
+        <v>-11.78937479957972</v>
       </c>
       <c r="F64">
-        <v>-0.7656692496965216</v>
+        <v>-1.03281111016014</v>
       </c>
       <c r="G64">
-        <v>-4.412253106989946</v>
+        <v>-4.415036160724073</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.157917179507425</v>
       </c>
       <c r="E65">
-        <v>-12.80625536677339</v>
+        <v>-11.68966450209323</v>
       </c>
       <c r="F65">
-        <v>-0.2512895407237518</v>
+        <v>-0.9826368965725737</v>
       </c>
       <c r="G65">
-        <v>-6.792513333365978</v>
+        <v>-4.571889695758159</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.357785899014495</v>
       </c>
       <c r="E66">
-        <v>-13.26871960100437</v>
+        <v>-11.16771382205673</v>
       </c>
       <c r="F66">
-        <v>-1.267697172326148</v>
+        <v>-1.445743976781665</v>
       </c>
       <c r="G66">
-        <v>-5.953814244215426</v>
+        <v>-4.641191910929261</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.535300272762639</v>
       </c>
       <c r="E67">
-        <v>-13.19611316062372</v>
+        <v>-11.45525310170859</v>
       </c>
       <c r="F67">
-        <v>-1.167014913087688</v>
+        <v>-0.9856861169822787</v>
       </c>
       <c r="G67">
-        <v>-5.370594788517447</v>
+        <v>-4.648428894935827</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.686926885004151</v>
       </c>
       <c r="E68">
-        <v>-13.35917654365914</v>
+        <v>-11.12811710528582</v>
       </c>
       <c r="F68">
-        <v>-1.808176253058922</v>
+        <v>-1.255144921071527</v>
       </c>
       <c r="G68">
-        <v>-5.893811501277869</v>
+        <v>-4.747757283649324</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.819118964103266</v>
       </c>
       <c r="E69">
-        <v>-12.99002250826308</v>
+        <v>-11.18131558914554</v>
       </c>
       <c r="F69">
-        <v>-1.620578372449126</v>
+        <v>-1.731776755866126</v>
       </c>
       <c r="G69">
-        <v>-5.533278116223489</v>
+        <v>-4.802632524209933</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.929664072217188</v>
       </c>
       <c r="E70">
-        <v>-13.12324922114093</v>
+        <v>-11.52724071360184</v>
       </c>
       <c r="F70">
-        <v>-1.700080105565406</v>
+        <v>-1.625237110722471</v>
       </c>
       <c r="G70">
-        <v>-5.283312375347347</v>
+        <v>-5.108744938262557</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.020023501728314</v>
       </c>
       <c r="E71">
-        <v>-11.85614597804899</v>
+        <v>-11.42395450116468</v>
       </c>
       <c r="F71">
-        <v>-1.539921066805941</v>
+        <v>-1.972931902536521</v>
       </c>
       <c r="G71">
-        <v>-5.242219255483224</v>
+        <v>-4.794105832375357</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.091311898608312</v>
       </c>
       <c r="E72">
-        <v>-11.72959762898146</v>
+        <v>-11.17889426694317</v>
       </c>
       <c r="F72">
-        <v>-2.01531614906816</v>
+        <v>-1.563257833277609</v>
       </c>
       <c r="G72">
-        <v>-5.925602538163855</v>
+        <v>-4.482654445633907</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.13852101131674</v>
       </c>
       <c r="E73">
-        <v>-11.83495629386971</v>
+        <v>-11.24070651109059</v>
       </c>
       <c r="F73">
-        <v>-1.749430921954589</v>
+        <v>-1.809495013964179</v>
       </c>
       <c r="G73">
-        <v>-5.502074496870502</v>
+        <v>-4.884620347349255</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.161951580548948</v>
       </c>
       <c r="E74">
-        <v>-12.64593725642368</v>
+        <v>-12.25397793764299</v>
       </c>
       <c r="F74">
-        <v>-1.765251082613254</v>
+        <v>-1.547486546295709</v>
       </c>
       <c r="G74">
-        <v>-5.571541188950845</v>
+        <v>-4.410028752598318</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.155295696611716</v>
       </c>
       <c r="E75">
-        <v>-12.89082720898087</v>
+        <v>-12.2967352482321</v>
       </c>
       <c r="F75">
-        <v>-1.517591595096078</v>
+        <v>-1.839415644553297</v>
       </c>
       <c r="G75">
-        <v>-5.296167681713989</v>
+        <v>-4.257099166684674</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.115287247790407</v>
       </c>
       <c r="E76">
-        <v>-12.44704411928897</v>
+        <v>-12.21737568623727</v>
       </c>
       <c r="F76">
-        <v>-2.249294320560701</v>
+        <v>-2.390031457194128</v>
       </c>
       <c r="G76">
-        <v>-3.982939655682686</v>
+        <v>-4.20924943981875</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.042101068676935</v>
       </c>
       <c r="E77">
-        <v>-14.10770151431033</v>
+        <v>-13.87403353875283</v>
       </c>
       <c r="F77">
-        <v>-2.576498616299102</v>
+        <v>-1.989427182628468</v>
       </c>
       <c r="G77">
-        <v>-4.16030581096915</v>
+        <v>-3.390715741889957</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.931350712150961</v>
       </c>
       <c r="E78">
-        <v>-13.5513871637722</v>
+        <v>-13.94661505986553</v>
       </c>
       <c r="F78">
-        <v>-1.931204551355302</v>
+        <v>-2.434389703246639</v>
       </c>
       <c r="G78">
-        <v>-3.426284526199285</v>
+        <v>-4.119544255668098</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.787008088666157</v>
       </c>
       <c r="E79">
-        <v>-15.85830085378219</v>
+        <v>-13.27035181305503</v>
       </c>
       <c r="F79">
-        <v>-1.975947159882711</v>
+        <v>-2.116442413234521</v>
       </c>
       <c r="G79">
-        <v>-3.477053065518074</v>
+        <v>-3.207723432009645</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.610349601415518</v>
       </c>
       <c r="E80">
-        <v>-15.69646266808759</v>
+        <v>-14.20143118748906</v>
       </c>
       <c r="F80">
-        <v>-2.268201806529599</v>
+        <v>-2.41681671716365</v>
       </c>
       <c r="G80">
-        <v>-3.21608303619039</v>
+        <v>-3.153707126419511</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.405575654679327</v>
       </c>
       <c r="E81">
-        <v>-16.82982835330873</v>
+        <v>-15.48372687760723</v>
       </c>
       <c r="F81">
-        <v>-2.125300145872656</v>
+        <v>-2.448734541560918</v>
       </c>
       <c r="G81">
-        <v>-3.362634573067943</v>
+        <v>-2.926877804109815</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.184375558640879</v>
       </c>
       <c r="E82">
-        <v>-16.18298645552331</v>
+        <v>-16.75036496103079</v>
       </c>
       <c r="F82">
-        <v>-1.833199575562689</v>
+        <v>-2.172620633757578</v>
       </c>
       <c r="G82">
-        <v>-2.786466738510561</v>
+        <v>-2.36451558695024</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.951563683825984</v>
       </c>
       <c r="E83">
-        <v>-17.77100418447343</v>
+        <v>-16.66213829285745</v>
       </c>
       <c r="F83">
-        <v>-2.546806615113157</v>
+        <v>-2.4662760496826</v>
       </c>
       <c r="G83">
-        <v>-2.128765350372711</v>
+        <v>-2.496057953173483</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.721822389621074</v>
       </c>
       <c r="E84">
-        <v>-19.72447543752918</v>
+        <v>-18.02994029773119</v>
       </c>
       <c r="F84">
-        <v>-2.519205413251878</v>
+        <v>-2.204588160199014</v>
       </c>
       <c r="G84">
-        <v>-2.219222428965604</v>
+        <v>-2.490058462103105</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.506835164474608</v>
       </c>
       <c r="E85">
-        <v>-19.61171159684876</v>
+        <v>-19.67410944379299</v>
       </c>
       <c r="F85">
-        <v>-1.919159260951194</v>
+        <v>-2.278780058263349</v>
       </c>
       <c r="G85">
-        <v>-1.707156206353826</v>
+        <v>-2.43456186432981</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.316305670558154</v>
       </c>
       <c r="E86">
-        <v>-20.20097752603808</v>
+        <v>-20.35468372395866</v>
       </c>
       <c r="F86">
-        <v>-2.096929390694176</v>
+        <v>-2.212061690907071</v>
       </c>
       <c r="G86">
-        <v>-2.437467623059719</v>
+        <v>-1.734707394023845</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.166010265577193</v>
       </c>
       <c r="E87">
-        <v>-23.64415999598526</v>
+        <v>-22.48583351070191</v>
       </c>
       <c r="F87">
-        <v>-2.233162693758583</v>
+        <v>-2.383419428584983</v>
       </c>
       <c r="G87">
-        <v>-2.622287454153811</v>
+        <v>-2.167884747325952</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.06398070414736</v>
       </c>
       <c r="E88">
-        <v>-23.61509166992279</v>
+        <v>-22.83888554579161</v>
       </c>
       <c r="F88">
-        <v>-3.075580036076971</v>
+        <v>-2.380711495545231</v>
       </c>
       <c r="G88">
-        <v>-2.644786851040025</v>
+        <v>-1.600100013650635</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.02138599453848</v>
       </c>
       <c r="E89">
-        <v>-25.15428839974954</v>
+        <v>-23.91733747087586</v>
       </c>
       <c r="F89">
-        <v>-2.514482062321115</v>
+        <v>-2.154526604578229</v>
       </c>
       <c r="G89">
-        <v>-1.425785818791183</v>
+        <v>-2.102060043950213</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.052212239463093</v>
       </c>
       <c r="E90">
-        <v>-26.12002632268928</v>
+        <v>-26.27654424467676</v>
       </c>
       <c r="F90">
-        <v>-1.996229735740257</v>
+        <v>-2.397924141808002</v>
       </c>
       <c r="G90">
-        <v>-2.257007735432786</v>
+        <v>-2.003663691055744</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.161000304920166</v>
       </c>
       <c r="E91">
-        <v>-28.14357678703453</v>
+        <v>-28.24849105831102</v>
       </c>
       <c r="F91">
-        <v>-2.699650341338499</v>
+        <v>-2.415609785857771</v>
       </c>
       <c r="G91">
-        <v>-2.418330865206859</v>
+        <v>-2.516719385867554</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.356720569095351</v>
       </c>
       <c r="E92">
-        <v>-29.29031373611594</v>
+        <v>-29.8640362719221</v>
       </c>
       <c r="F92">
-        <v>-2.225694961622346</v>
+        <v>-1.752899296270111</v>
       </c>
       <c r="G92">
-        <v>-2.699077284812226</v>
+        <v>-2.167634115845205</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.644499088681742</v>
       </c>
       <c r="E93">
-        <v>-31.7727525197415</v>
+        <v>-31.38514576642923</v>
       </c>
       <c r="F93">
-        <v>-2.127732232567276</v>
+        <v>-1.887850286594984</v>
       </c>
       <c r="G93">
-        <v>-3.120438408094954</v>
+        <v>-2.602448406005941</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.017639190420956</v>
       </c>
       <c r="E94">
-        <v>-32.54571706243365</v>
+        <v>-33.41532890926023</v>
       </c>
       <c r="F94">
-        <v>-2.663782861164683</v>
+        <v>-1.92814456216936</v>
       </c>
       <c r="G94">
-        <v>-2.405762740745239</v>
+        <v>-2.292803654521541</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.47841477358433</v>
       </c>
       <c r="E95">
-        <v>-34.16254977155543</v>
+        <v>-35.60219817913737</v>
       </c>
       <c r="F95">
-        <v>-2.639548144428381</v>
+        <v>-1.901513378536759</v>
       </c>
       <c r="G95">
-        <v>-2.959402460225905</v>
+        <v>-3.277506024185512</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.017256052693329</v>
       </c>
       <c r="E96">
-        <v>-36.92063926741552</v>
+        <v>-37.32344054435968</v>
       </c>
       <c r="F96">
-        <v>-3.166780802022988</v>
+        <v>-1.79142500743951</v>
       </c>
       <c r="G96">
-        <v>-3.209838135128447</v>
+        <v>-3.298279718897001</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.614995823695264</v>
       </c>
       <c r="E97">
-        <v>-40.96498869360332</v>
+        <v>-39.1961546798098</v>
       </c>
       <c r="F97">
-        <v>-2.451568386445895</v>
+        <v>-1.576995478285636</v>
       </c>
       <c r="G97">
-        <v>-4.42150036433167</v>
+        <v>-4.095807365845696</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.27221445251878</v>
       </c>
       <c r="E98">
-        <v>-41.46924461679038</v>
+        <v>-41.79544198745374</v>
       </c>
       <c r="F98">
-        <v>-2.140873453045287</v>
+        <v>-1.353632835059972</v>
       </c>
       <c r="G98">
-        <v>-4.981100413713847</v>
+        <v>-4.224269053451425</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.94720712737629</v>
       </c>
       <c r="E99">
-        <v>-43.78317723393933</v>
+        <v>-43.84736303835889</v>
       </c>
       <c r="F99">
-        <v>-1.727489126189236</v>
+        <v>-1.294940519469418</v>
       </c>
       <c r="G99">
-        <v>-5.19390220533549</v>
+        <v>-4.479304860323508</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.65602918860961</v>
       </c>
       <c r="E100">
-        <v>-44.89387676835521</v>
+        <v>-45.91446407665629</v>
       </c>
       <c r="F100">
-        <v>-2.366063474761527</v>
+        <v>-1.279881628453926</v>
       </c>
       <c r="G100">
-        <v>-4.239460976227114</v>
+        <v>-5.029853458208296</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.33139669090424</v>
       </c>
       <c r="E101">
-        <v>-47.18841285031439</v>
+        <v>-47.70426038630905</v>
       </c>
       <c r="F101">
-        <v>-1.985490780730364</v>
+        <v>-1.22009669625908</v>
       </c>
       <c r="G101">
-        <v>-5.369840283330615</v>
+        <v>-5.493184911537762</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.0281574680002</v>
       </c>
       <c r="E102">
-        <v>-48.82183867698168</v>
+        <v>-50.47723706816299</v>
       </c>
       <c r="F102">
-        <v>-1.918195041294335</v>
+        <v>-1.096119088919092</v>
       </c>
       <c r="G102">
-        <v>-6.486173784533927</v>
+        <v>-5.198763411764143</v>
       </c>
     </row>
   </sheetData>
